--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246434</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>132246435</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>132246437</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246434</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>132246435</v>
       </c>
       <c r="B3" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>132246437</v>
       </c>
       <c r="B4" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>132246433</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246434</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>132246435</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>132246437</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>132246433</v>
       </c>
       <c r="B5" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246434</v>
       </c>
       <c r="B2" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>132246435</v>
       </c>
       <c r="B3" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>132246437</v>
       </c>
       <c r="B4" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246434</v>
       </c>
       <c r="B2" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>132246435</v>
       </c>
       <c r="B3" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>132246437</v>
       </c>
       <c r="B4" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>132246433</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246434</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>132246435</v>
       </c>
       <c r="B3" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>132246437</v>
       </c>
       <c r="B4" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246434</v>
       </c>
       <c r="B2" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>132246435</v>
       </c>
       <c r="B3" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>132246437</v>
       </c>
       <c r="B4" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132246434</v>
+        <v>132246433</v>
       </c>
       <c r="B2" t="n">
-        <v>91933</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767398</v>
+        <v>767390</v>
       </c>
       <c r="R2" t="n">
-        <v>7102561</v>
+        <v>7102552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,289 +769,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>132246435</v>
-      </c>
-      <c r="B3" t="n">
-        <v>91933</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tväråmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>767405</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7102527</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>132246437</v>
-      </c>
-      <c r="B4" t="n">
-        <v>91933</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tväråmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>767431</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7102414</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>132246433</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57951</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Tväråmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>767390</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7102552</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5912-2026 artfynd.xlsx
+++ b/artfynd/A 5912-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,8 +774,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132246433</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>